--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -1,31 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\IntegrationPSP\Integration\src\test\resources\ExcelResultsFolder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C7A6A8-E924-4D41-A560-07BA2B31C148}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA18E017-9ED3-463E-908A-0A5FBD8E1EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cards" sheetId="23" r:id="rId1"/>
-    <sheet name="CreateCustomerSession" sheetId="25" r:id="rId2"/>
-    <sheet name="CardDataForEndtoEndFlow" sheetId="24" r:id="rId3"/>
+    <sheet name="CardDataForEndtoEndFlow" sheetId="24" r:id="rId2"/>
+    <sheet name="newLogic" sheetId="25" r:id="rId3"/>
+    <sheet name="CC" sheetId="26" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="49">
-  <si>
-    <t>Easybuzz</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="81">
   <si>
     <t>Matrix</t>
   </si>
@@ -54,9 +52,6 @@
     <t>Currency</t>
   </si>
   <si>
-    <t>AB de Villiers</t>
-  </si>
-  <si>
     <t>4111111111111111</t>
   </si>
   <si>
@@ -72,9 +67,6 @@
     <t>INR</t>
   </si>
   <si>
-    <t>Virat Kohli</t>
-  </si>
-  <si>
     <t>5553042241984105</t>
   </si>
   <si>
@@ -99,9 +91,6 @@
     <t>EUR</t>
   </si>
   <si>
-    <t>KL Rahul</t>
-  </si>
-  <si>
     <t>4999992100017063</t>
   </si>
   <si>
@@ -127,9 +116,6 @@
   </si>
   <si>
     <t>Visa</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <r>
@@ -191,12 +177,123 @@
   <si>
     <t>Payu</t>
   </si>
+  <si>
+    <t>Merchant</t>
+  </si>
+  <si>
+    <t>RouteToMidOrBank</t>
+  </si>
+  <si>
+    <t>SuhasM</t>
+  </si>
+  <si>
+    <t>easebuzz_card</t>
+  </si>
+  <si>
+    <t>zaakpay_sandbox</t>
+  </si>
+  <si>
+    <t>euroExchangeMid</t>
+  </si>
+  <si>
+    <t>matrix</t>
+  </si>
+  <si>
+    <t>monnet-Peru</t>
+  </si>
+  <si>
+    <t>payu_indian_orch_sandbox</t>
+  </si>
+  <si>
+    <t>RouteToBankMid</t>
+  </si>
+  <si>
+    <t>Route to Mid</t>
+  </si>
+  <si>
+    <t>PartialMerchant</t>
+  </si>
+  <si>
+    <t>Suhas</t>
+  </si>
+  <si>
+    <t>Tokyo</t>
+  </si>
+  <si>
+    <t>Divanshu Bahubali</t>
+  </si>
+  <si>
+    <t>paynetics</t>
+  </si>
+  <si>
+    <t>panatics-mid</t>
+  </si>
+  <si>
+    <t>TestData</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>zaakpay-sandbox</t>
+  </si>
+  <si>
+    <t>euroexchange</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>4456530000001096</t>
+  </si>
+  <si>
+    <t>02/29</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>telr</t>
+  </si>
+  <si>
+    <t>5200000000001096</t>
+  </si>
+  <si>
+    <t>CAD</t>
+  </si>
+  <si>
+    <t>INTERAC</t>
+  </si>
+  <si>
+    <t>4387751111111111</t>
+  </si>
+  <si>
+    <t>mantapay</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>mantapay-card</t>
+  </si>
+  <si>
+    <t>4570020000000851</t>
+  </si>
+  <si>
+    <t>pxp</t>
+  </si>
+  <si>
+    <t>pxp_sandbox</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -208,18 +305,6 @@
       <sz val="9"/>
       <color rgb="FF1C1E1F"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF1C1E1F"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF292A2E"/>
-      <name val="Segoe UI"/>
       <family val="2"/>
     </font>
     <font>
@@ -253,6 +338,24 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF292A2E"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF232323"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -274,11 +377,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -286,15 +388,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="17" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="17" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -597,204 +707,400 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.7265625" style="4" customWidth="1"/>
     <col min="5" max="5" width="17.453125" customWidth="1"/>
     <col min="6" max="6" width="17.90625" customWidth="1"/>
     <col min="7" max="7" width="11.90625" customWidth="1"/>
-    <col min="8" max="8" width="11.26953125" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="8" max="8" width="16.453125" customWidth="1"/>
+    <col min="9" max="9" width="11.26953125" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" customWidth="1"/>
+    <col min="11" max="11" width="25.26953125" customWidth="1"/>
+    <col min="12" max="12" width="17.7265625" customWidth="1"/>
+    <col min="13" max="13" width="16.90625" customWidth="1"/>
+    <col min="14" max="14" width="19.36328125" customWidth="1"/>
+    <col min="15" max="15" width="11.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="H1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" t="s">
         <v>44</v>
       </c>
+      <c r="J1" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="K1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="6">
         <v>123</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" s="5">
-        <v>10</v>
-      </c>
-      <c r="I2" s="5">
-        <v>100</v>
-      </c>
-      <c r="J2" s="5">
-        <v>10</v>
-      </c>
-      <c r="K2" t="b">
+      <c r="H2" t="s">
+        <v>56</v>
+      </c>
+      <c r="I2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K2" t="s">
+        <v>47</v>
+      </c>
+      <c r="L2" s="4">
+        <v>10</v>
+      </c>
+      <c r="M2" s="4">
+        <v>100</v>
+      </c>
+      <c r="N2" s="4">
+        <v>100</v>
+      </c>
+      <c r="O2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="4">
+        <v>123</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="4">
+        <v>10</v>
+      </c>
+      <c r="M3" s="4">
+        <v>100</v>
+      </c>
+      <c r="N3" s="4">
+        <v>500</v>
+      </c>
+      <c r="O3" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" t="s">
+        <v>46</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" t="s">
+        <v>70</v>
+      </c>
+      <c r="L4" s="4">
+        <v>10</v>
+      </c>
+      <c r="M4" s="4">
+        <v>100</v>
+      </c>
+      <c r="N4" s="4">
+        <v>100</v>
+      </c>
+      <c r="O4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K5" t="s">
+        <v>70</v>
+      </c>
+      <c r="L5" s="4">
+        <v>10</v>
+      </c>
+      <c r="M5" s="4">
+        <v>100</v>
+      </c>
+      <c r="N5" s="4">
+        <v>100</v>
+      </c>
+      <c r="O5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="5">
-        <v>123</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" t="s">
         <v>0</v>
       </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H3" s="5">
-        <v>10</v>
-      </c>
-      <c r="I3" s="5">
-        <v>100</v>
-      </c>
-      <c r="J3" s="5">
-        <v>500</v>
-      </c>
-      <c r="K3" t="b">
+      <c r="F6" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="G6" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K6" t="s">
+        <v>50</v>
+      </c>
+      <c r="L6" s="4">
+        <v>10</v>
+      </c>
+      <c r="M6" s="4">
+        <v>100</v>
+      </c>
+      <c r="N6" s="4">
+        <v>100</v>
+      </c>
+      <c r="O6" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="5">
-        <v>10</v>
-      </c>
-      <c r="I4" s="5">
-        <v>100</v>
-      </c>
-      <c r="J4" s="5">
-        <v>10</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="5">
-        <v>870</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="5">
-        <v>10</v>
-      </c>
-      <c r="I5" s="5">
-        <v>100</v>
-      </c>
-      <c r="J5" s="5">
-        <v>500</v>
-      </c>
-      <c r="K5" t="b">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" t="s">
+        <v>77</v>
+      </c>
+      <c r="L7" s="4">
+        <v>10</v>
+      </c>
+      <c r="M7" s="4">
+        <v>100</v>
+      </c>
+      <c r="N7" s="4">
+        <v>55.3</v>
+      </c>
+      <c r="O7" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G9" t="s">
-        <v>35</v>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="4">
+        <v>10</v>
+      </c>
+      <c r="M8" s="4">
+        <v>100</v>
+      </c>
+      <c r="N8" s="4">
+        <v>55.3</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -804,299 +1110,1062 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEE785E9-817D-4E9B-B308-F1BE7846862A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5638B9FC-7E5E-4870-A731-709F452B5553}">
+  <dimension ref="A1:P9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="13.36328125" customWidth="1"/>
+    <col min="2" max="2" width="17.36328125" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="23.90625" customWidth="1"/>
+    <col min="7" max="7" width="16.54296875" customWidth="1"/>
+    <col min="8" max="8" width="17.90625" customWidth="1"/>
+    <col min="9" max="10" width="11.90625" customWidth="1"/>
+    <col min="11" max="11" width="16.54296875" customWidth="1"/>
+    <col min="12" max="12" width="24.7265625" customWidth="1"/>
+    <col min="13" max="13" width="14.6328125" style="4" customWidth="1"/>
+    <col min="14" max="14" width="11.90625" style="4" customWidth="1"/>
+    <col min="15" max="15" width="15.36328125" style="4" customWidth="1"/>
+    <col min="16" max="16" width="15.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="6">
+        <v>123</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="4">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4">
+        <v>100</v>
+      </c>
+      <c r="O2" s="4">
+        <v>500</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9">
+        <v>123</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" t="s">
+        <v>64</v>
+      </c>
+      <c r="M3" s="4">
+        <v>10</v>
+      </c>
+      <c r="N3" s="4">
+        <v>100</v>
+      </c>
+      <c r="O3" s="4">
+        <v>500</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4">
+        <v>870</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>46</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M4" s="4">
+        <v>10</v>
+      </c>
+      <c r="N4" s="4">
+        <v>100</v>
+      </c>
+      <c r="O4" s="4">
+        <v>500</v>
+      </c>
+      <c r="P4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>46</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M5" s="4">
+        <v>10</v>
+      </c>
+      <c r="N5" s="4">
+        <v>100</v>
+      </c>
+      <c r="O5" s="4">
+        <v>500</v>
+      </c>
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6">
+        <v>123</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" t="s">
+        <v>46</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" s="4">
+        <v>10</v>
+      </c>
+      <c r="N6" s="4">
+        <v>100</v>
+      </c>
+      <c r="O6" s="4">
+        <v>500</v>
+      </c>
+      <c r="P6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7">
+        <v>123</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="4">
+        <v>10</v>
+      </c>
+      <c r="N7" s="4">
+        <v>900</v>
+      </c>
+      <c r="O7" s="4">
+        <v>10</v>
+      </c>
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="9">
+        <v>123</v>
+      </c>
+      <c r="G8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
+        <v>46</v>
+      </c>
+      <c r="K8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" t="s">
+        <v>48</v>
+      </c>
+      <c r="M8" s="4">
+        <v>10</v>
+      </c>
+      <c r="N8" s="4">
+        <v>100</v>
+      </c>
+      <c r="O8" s="4">
+        <v>500</v>
+      </c>
+      <c r="P8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="4">
+        <v>123</v>
+      </c>
+      <c r="G9" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L9" t="s">
+        <v>60</v>
+      </c>
+      <c r="M9" s="4">
+        <v>10</v>
+      </c>
+      <c r="N9" s="4">
+        <v>100</v>
+      </c>
+      <c r="O9" s="4">
+        <v>500</v>
+      </c>
+      <c r="P9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2073F329-CD68-4CCD-9057-C4D46B09DCF7}">
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="16.6328125" customWidth="1"/>
+    <col min="2" max="2" width="15.6328125" customWidth="1"/>
+    <col min="3" max="3" width="18.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.6328125" customWidth="1"/>
+    <col min="6" max="6" width="14.81640625" customWidth="1"/>
+    <col min="7" max="7" width="11.54296875" customWidth="1"/>
+    <col min="8" max="8" width="14.36328125" customWidth="1"/>
+    <col min="9" max="9" width="13.36328125" customWidth="1"/>
+    <col min="10" max="10" width="14.7265625" customWidth="1"/>
+    <col min="11" max="11" width="11.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="6">
+        <v>123</v>
+      </c>
+      <c r="F2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="4">
+        <v>10</v>
+      </c>
+      <c r="I2" s="4">
+        <v>100</v>
+      </c>
+      <c r="J2" s="4">
+        <v>500</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9">
+        <v>123</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="4">
+        <v>10</v>
+      </c>
+      <c r="I3" s="4">
+        <v>100</v>
+      </c>
+      <c r="J3" s="4">
+        <v>500</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>870</v>
+      </c>
+      <c r="F4" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="4">
+        <v>10</v>
+      </c>
+      <c r="I4" s="4">
+        <v>100</v>
+      </c>
+      <c r="J4" s="4">
+        <v>500</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" t="s">
+        <v>21</v>
+      </c>
+      <c r="H5" s="4">
+        <v>10</v>
+      </c>
+      <c r="I5" s="4">
+        <v>100</v>
+      </c>
+      <c r="J5" s="4">
+        <v>500</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6">
+        <v>123</v>
+      </c>
+      <c r="F6" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" s="4">
+        <v>10</v>
+      </c>
+      <c r="I6" s="4">
+        <v>100</v>
+      </c>
+      <c r="J6" s="4">
+        <v>500</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7">
+        <v>123</v>
+      </c>
+      <c r="F7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7" s="4">
+        <v>10</v>
+      </c>
+      <c r="I7" s="4">
+        <v>900</v>
+      </c>
+      <c r="J7" s="4">
+        <v>10</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10">
+        <v>870</v>
+      </c>
+      <c r="E10" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="4">
+        <v>10</v>
+      </c>
+      <c r="M10" s="4">
+        <v>100</v>
+      </c>
+      <c r="N10" s="4">
+        <v>100</v>
+      </c>
+      <c r="O10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" t="s">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="4">
+        <v>10</v>
+      </c>
+      <c r="M12" s="4">
+        <v>100</v>
+      </c>
+      <c r="N12" s="4">
+        <v>100</v>
+      </c>
+      <c r="O12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13">
+        <v>123</v>
+      </c>
+      <c r="E13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" t="s">
+        <v>52</v>
+      </c>
+      <c r="L13" s="4">
+        <v>10</v>
+      </c>
+      <c r="M13" s="4">
+        <v>900</v>
+      </c>
+      <c r="N13" s="4">
+        <v>10</v>
+      </c>
+      <c r="O13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5638B9FC-7E5E-4870-A731-709F452B5553}">
-  <dimension ref="A1:L7"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{079DCA6A-1D13-412F-9799-ED3200D08D62}">
+  <dimension ref="A1:P3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.36328125" customWidth="1"/>
-    <col min="2" max="2" width="19.36328125" customWidth="1"/>
-    <col min="3" max="3" width="23.90625" customWidth="1"/>
-    <col min="6" max="6" width="16.54296875" customWidth="1"/>
-    <col min="7" max="7" width="17.90625" customWidth="1"/>
-    <col min="8" max="8" width="11.90625" customWidth="1"/>
-    <col min="9" max="9" width="14.6328125" customWidth="1"/>
-    <col min="10" max="10" width="11.90625" customWidth="1"/>
-    <col min="11" max="11" width="15.36328125" customWidth="1"/>
-    <col min="12" max="12" width="15.90625" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="26.453125" customWidth="1"/>
+    <col min="5" max="5" width="9.36328125" customWidth="1"/>
+    <col min="6" max="6" width="12.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.6328125" customWidth="1"/>
+    <col min="9" max="9" width="15.7265625" customWidth="1"/>
+    <col min="10" max="10" width="24" customWidth="1"/>
+    <col min="11" max="11" width="18.90625" customWidth="1"/>
+    <col min="12" max="12" width="19.7265625" customWidth="1"/>
+    <col min="13" max="13" width="14.7265625" customWidth="1"/>
+    <col min="14" max="14" width="13.90625" customWidth="1"/>
+    <col min="15" max="15" width="14.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>44</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="6">
+        <v>123</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L2" t="s">
+        <v>47</v>
+      </c>
+      <c r="M2" s="4">
+        <v>10</v>
+      </c>
+      <c r="N2" s="4">
+        <v>100</v>
+      </c>
+      <c r="O2" s="4">
+        <v>500</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="4">
+        <v>123</v>
+      </c>
+      <c r="G3" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="8">
-        <v>123</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="5">
-        <v>10</v>
-      </c>
-      <c r="J2" s="5">
-        <v>100</v>
-      </c>
-      <c r="K2" s="5">
-        <v>500</v>
-      </c>
-      <c r="L2" t="b">
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>46</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M3" s="4">
+        <v>10</v>
+      </c>
+      <c r="N3" s="4">
+        <v>100</v>
+      </c>
+      <c r="O3" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="P3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="11">
-        <v>123</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" t="s">
-        <v>34</v>
-      </c>
-      <c r="H3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="5">
-        <v>10</v>
-      </c>
-      <c r="J3" s="5">
-        <v>100</v>
-      </c>
-      <c r="K3" s="5">
-        <v>500</v>
-      </c>
-      <c r="L3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4">
-        <v>870</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5">
-        <v>10</v>
-      </c>
-      <c r="J4" s="5">
-        <v>100</v>
-      </c>
-      <c r="K4" s="5">
-        <v>500</v>
-      </c>
-      <c r="L4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="5">
-        <v>10</v>
-      </c>
-      <c r="J5" s="5">
-        <v>100</v>
-      </c>
-      <c r="K5" s="5">
-        <v>500</v>
-      </c>
-      <c r="L5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6">
-        <v>123</v>
-      </c>
-      <c r="F6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" t="s">
-        <v>41</v>
-      </c>
-      <c r="I6" s="5">
-        <v>10</v>
-      </c>
-      <c r="J6" s="5">
-        <v>100</v>
-      </c>
-      <c r="K6" s="5">
-        <v>500</v>
-      </c>
-      <c r="L6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" t="s">
-        <v>45</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7">
-        <v>123</v>
-      </c>
-      <c r="F7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G7" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I7" s="5">
-        <v>10</v>
-      </c>
-      <c r="J7" s="5">
-        <v>900</v>
-      </c>
-      <c r="K7" s="5">
-        <v>10</v>
-      </c>
-      <c r="L7" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA18E017-9ED3-463E-908A-0A5FBD8E1EE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536182D8-FB84-49C2-B300-348AD435CEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="77">
   <si>
     <t>Matrix</t>
   </si>
@@ -244,22 +244,10 @@
     <t>euroexchange</t>
   </si>
   <si>
-    <t>AED</t>
-  </si>
-  <si>
-    <t>4456530000001096</t>
-  </si>
-  <si>
     <t>02/29</t>
   </si>
   <si>
     <t>123</t>
-  </si>
-  <si>
-    <t>telr</t>
-  </si>
-  <si>
-    <t>5200000000001096</t>
   </si>
   <si>
     <t>CAD</t>
@@ -707,7 +695,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -865,7 +853,7 @@
         <v>500</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -873,22 +861,22 @@
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" t="s">
         <v>68</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" t="s">
-        <v>66</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>56</v>
@@ -900,7 +888,7 @@
         <v>54</v>
       </c>
       <c r="K4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="L4" s="4">
         <v>10</v>
@@ -912,7 +900,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -920,22 +908,22 @@
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E5" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E5" t="s">
-        <v>70</v>
-      </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>56</v>
@@ -947,7 +935,7 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L5" s="4">
         <v>10</v>
@@ -956,10 +944,10 @@
         <v>100</v>
       </c>
       <c r="N5" s="4">
-        <v>100</v>
+        <v>55.3</v>
       </c>
       <c r="O5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
@@ -967,19 +955,19 @@
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" t="s">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
       </c>
       <c r="G6" t="s">
         <v>72</v>
@@ -993,114 +981,20 @@
       <c r="J6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K6" t="s">
-        <v>50</v>
+      <c r="K6" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="L6" s="4">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M6" s="4">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="N6" s="4">
-        <v>100</v>
+        <v>569</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="F7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" t="s">
-        <v>76</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K7" t="s">
-        <v>77</v>
-      </c>
-      <c r="L7" s="4">
-        <v>10</v>
-      </c>
-      <c r="M7" s="4">
-        <v>100</v>
-      </c>
-      <c r="N7" s="4">
-        <v>55.3</v>
-      </c>
-      <c r="O7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="F8" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" t="s">
-        <v>76</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="I8" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="L8" s="4">
-        <v>10</v>
-      </c>
-      <c r="M8" s="4">
-        <v>100</v>
-      </c>
-      <c r="N8" s="4">
-        <v>55.3</v>
-      </c>
-      <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1226,7 +1120,7 @@
         <v>500</v>
       </c>
       <c r="P2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -1276,7 +1170,7 @@
         <v>500</v>
       </c>
       <c r="P3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -1376,7 +1270,7 @@
         <v>500</v>
       </c>
       <c r="P5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -1476,7 +1370,7 @@
         <v>10</v>
       </c>
       <c r="P7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{536182D8-FB84-49C2-B300-348AD435CEC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3315B4-470B-40F5-808B-4A6D3DA939C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="82">
   <si>
     <t>Matrix</t>
   </si>
@@ -276,12 +276,27 @@
   <si>
     <t>pxp_sandbox</t>
   </si>
+  <si>
+    <t>4000000000001000</t>
+  </si>
+  <si>
+    <t>payIn</t>
+  </si>
+  <si>
+    <t>payerworld_cards_payin_mid</t>
+  </si>
+  <si>
+    <t>4000000000001091</t>
+  </si>
+  <si>
+    <t>HKD</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -344,6 +359,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF232323"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -388,11 +409,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,7 +714,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -772,8 +791,8 @@
       <c r="C2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="6">
-        <v>123</v>
+      <c r="D2" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>29</v>
@@ -806,7 +825,7 @@
         <v>100</v>
       </c>
       <c r="O2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
@@ -819,8 +838,8 @@
       <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4">
-        <v>123</v>
+      <c r="D3" s="5" t="s">
+        <v>67</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>59</v>
@@ -840,7 +859,7 @@
       <c r="J3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="14" t="s">
+      <c r="K3" s="15" t="s">
         <v>60</v>
       </c>
       <c r="L3" s="4">
@@ -850,10 +869,10 @@
         <v>100</v>
       </c>
       <c r="N3" s="4">
-        <v>500</v>
+        <v>13</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -872,7 +891,7 @@
       <c r="E4" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="15" t="s">
+      <c r="F4" s="14" t="s">
         <v>69</v>
       </c>
       <c r="G4" t="s">
@@ -900,7 +919,7 @@
         <v>100</v>
       </c>
       <c r="O4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
@@ -981,7 +1000,7 @@
       <c r="J6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="16" t="s">
+      <c r="K6" s="15" t="s">
         <v>76</v>
       </c>
       <c r="L6" s="4">
@@ -994,6 +1013,147 @@
         <v>569</v>
       </c>
       <c r="O6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" t="s">
+        <v>72</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L7" s="4">
+        <v>100</v>
+      </c>
+      <c r="M7" s="4">
+        <v>900</v>
+      </c>
+      <c r="N7" s="4">
+        <v>569</v>
+      </c>
+      <c r="O7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L8" s="4">
+        <v>100</v>
+      </c>
+      <c r="M8" s="4">
+        <v>900</v>
+      </c>
+      <c r="N8" s="4">
+        <v>569</v>
+      </c>
+      <c r="O8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" t="s">
+        <v>81</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="L9" s="4">
+        <v>100</v>
+      </c>
+      <c r="M9" s="4">
+        <v>900</v>
+      </c>
+      <c r="N9" s="4">
+        <v>569</v>
+      </c>
+      <c r="O9" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3315B4-470B-40F5-808B-4A6D3DA939C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCA6DBC-46D8-4B60-98CE-1F87700A9F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -966,7 +966,7 @@
         <v>55.3</v>
       </c>
       <c r="O5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCA6DBC-46D8-4B60-98CE-1F87700A9F4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A310ABE-7A3C-42CD-8FE1-9B1FA075DE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="89">
   <si>
     <t>Matrix</t>
   </si>
@@ -280,9 +280,6 @@
     <t>4000000000001000</t>
   </si>
   <si>
-    <t>payIn</t>
-  </si>
-  <si>
     <t>payerworld_cards_payin_mid</t>
   </si>
   <si>
@@ -290,6 +287,30 @@
   </si>
   <si>
     <t>HKD</t>
+  </si>
+  <si>
+    <t>payerworld_payin</t>
+  </si>
+  <si>
+    <t>GBP</t>
+  </si>
+  <si>
+    <t>trustpayments-network-token</t>
+  </si>
+  <si>
+    <t>trustpayments</t>
+  </si>
+  <si>
+    <t>4900490000000543</t>
+  </si>
+  <si>
+    <t>4900490000000626</t>
+  </si>
+  <si>
+    <t>Sikandar raza</t>
+  </si>
+  <si>
+    <t>4900490000000576</t>
   </si>
 </sst>
 </file>
@@ -714,14 +735,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" style="4" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="5" max="5" width="20.08984375" customWidth="1"/>
     <col min="6" max="6" width="17.90625" customWidth="1"/>
     <col min="7" max="7" width="11.90625" customWidth="1"/>
     <col min="8" max="8" width="16.453125" customWidth="1"/>
@@ -1013,7 +1034,7 @@
         <v>569</v>
       </c>
       <c r="O6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -1029,8 +1050,8 @@
       <c r="D7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>78</v>
+      <c r="E7" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1048,7 +1069,7 @@
         <v>54</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L7" s="4">
         <v>100</v>
@@ -1060,7 +1081,7 @@
         <v>569</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1068,7 +1089,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>66</v>
@@ -1076,8 +1097,8 @@
       <c r="D8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>78</v>
+      <c r="E8" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
@@ -1095,7 +1116,7 @@
         <v>54</v>
       </c>
       <c r="K8" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L8" s="4">
         <v>100</v>
@@ -1123,14 +1144,14 @@
       <c r="D9" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>78</v>
+      <c r="E9" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>56</v>
@@ -1142,7 +1163,7 @@
         <v>54</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="L9" s="4">
         <v>100</v>
@@ -1154,7 +1175,148 @@
         <v>569</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" t="s">
+        <v>82</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L10" s="4">
+        <v>100</v>
+      </c>
+      <c r="M10" s="4">
+        <v>900</v>
+      </c>
+      <c r="N10" s="4">
+        <v>569</v>
+      </c>
+      <c r="O10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L11" s="4">
+        <v>100</v>
+      </c>
+      <c r="M11" s="4">
+        <v>900</v>
+      </c>
+      <c r="N11" s="4">
+        <v>569</v>
+      </c>
+      <c r="O11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="L12" s="4">
+        <v>100</v>
+      </c>
+      <c r="M12" s="4">
+        <v>900</v>
+      </c>
+      <c r="N12" s="4">
+        <v>569</v>
+      </c>
+      <c r="O12" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A310ABE-7A3C-42CD-8FE1-9B1FA075DE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BB6613-052D-4C7B-AFF9-6486A050F656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1081,7 +1081,7 @@
         <v>569</v>
       </c>
       <c r="O7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1128,7 +1128,7 @@
         <v>569</v>
       </c>
       <c r="O8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1175,7 +1175,7 @@
         <v>569</v>
       </c>
       <c r="O9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
@@ -1222,7 +1222,7 @@
         <v>569</v>
       </c>
       <c r="O10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
@@ -1269,7 +1269,7 @@
         <v>569</v>
       </c>
       <c r="O11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
@@ -1316,7 +1316,7 @@
         <v>569</v>
       </c>
       <c r="O12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61BB6613-052D-4C7B-AFF9-6486A050F656}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEC88B9-BF7F-47E0-B116-17A27B86481F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1034,7 +1034,7 @@
         <v>569</v>
       </c>
       <c r="O6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
@@ -1081,7 +1081,7 @@
         <v>569</v>
       </c>
       <c r="O7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
@@ -1128,7 +1128,7 @@
         <v>569</v>
       </c>
       <c r="O8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
@@ -1175,7 +1175,7 @@
         <v>569</v>
       </c>
       <c r="O9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFEC88B9-BF7F-47E0-B116-17A27B86481F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A9A697-9D21-4586-86B8-31DECFFC7393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -893,7 +893,7 @@
         <v>13</v>
       </c>
       <c r="O3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -1222,7 +1222,7 @@
         <v>569</v>
       </c>
       <c r="O10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
@@ -1269,7 +1269,7 @@
         <v>569</v>
       </c>
       <c r="O11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
@@ -1316,7 +1316,7 @@
         <v>569</v>
       </c>
       <c r="O12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A9A697-9D21-4586-86B8-31DECFFC7393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9455579D-653C-447F-82E1-B64D0D600429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
   <si>
     <t>Matrix</t>
   </si>
@@ -311,6 +311,30 @@
   </si>
   <si>
     <t>4900490000000576</t>
+  </si>
+  <si>
+    <t>`</t>
+  </si>
+  <si>
+    <t>4100000000000100</t>
+  </si>
+  <si>
+    <t>196</t>
+  </si>
+  <si>
+    <t>08/27</t>
+  </si>
+  <si>
+    <t>unicornpayment</t>
+  </si>
+  <si>
+    <t>Brian Bennet</t>
+  </si>
+  <si>
+    <t>4100000000005000</t>
+  </si>
+  <si>
+    <t>unicornpayment3ds</t>
   </si>
 </sst>
 </file>
@@ -735,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -893,7 +917,7 @@
         <v>13</v>
       </c>
       <c r="O3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -1191,7 +1215,7 @@
       <c r="D10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" t="s">
         <v>84</v>
       </c>
       <c r="F10" t="s">
@@ -1238,7 +1262,7 @@
       <c r="D11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" t="s">
         <v>84</v>
       </c>
       <c r="F11" t="s">
@@ -1285,7 +1309,7 @@
       <c r="D12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" t="s">
         <v>84</v>
       </c>
       <c r="F12" t="s">
@@ -1317,6 +1341,105 @@
       </c>
       <c r="O12" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" t="s">
+        <v>72</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J13" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K13" t="s">
+        <v>93</v>
+      </c>
+      <c r="L13" s="4">
+        <v>100</v>
+      </c>
+      <c r="M13" s="4">
+        <v>900</v>
+      </c>
+      <c r="N13" s="4">
+        <v>569</v>
+      </c>
+      <c r="O13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" t="s">
+        <v>72</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" t="s">
+        <v>46</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K14" t="s">
+        <v>93</v>
+      </c>
+      <c r="L14" s="4">
+        <v>100</v>
+      </c>
+      <c r="M14" s="4">
+        <v>900</v>
+      </c>
+      <c r="N14" s="4">
+        <v>569</v>
+      </c>
+      <c r="O14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E17" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9455579D-653C-447F-82E1-B64D0D600429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E48FA4-4297-43D1-8D3F-D93E833437AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,7 +334,7 @@
     <t>4100000000005000</t>
   </si>
   <si>
-    <t>unicornpayment3ds</t>
+    <t>unicornpaymentds</t>
   </si>
 </sst>
 </file>
@@ -1387,7 +1387,7 @@
         <v>569</v>
       </c>
       <c r="O13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93E48FA4-4297-43D1-8D3F-D93E833437AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584731D3-684E-4EDD-AA21-197729E55E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="106">
   <si>
     <t>Matrix</t>
   </si>
@@ -335,6 +335,33 @@
   </si>
   <si>
     <t>unicornpaymentds</t>
+  </si>
+  <si>
+    <t>Mighty Sanju</t>
+  </si>
+  <si>
+    <t>4508750015741019</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>01/39</t>
+  </si>
+  <si>
+    <t>ccavenue_mid</t>
+  </si>
+  <si>
+    <t>ccavenue</t>
+  </si>
+  <si>
+    <t>AED</t>
+  </si>
+  <si>
+    <t>ak bihari sab pe bhari</t>
+  </si>
+  <si>
+    <t>5123450000000008</t>
   </si>
 </sst>
 </file>
@@ -759,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -1434,11 +1461,105 @@
         <v>569</v>
       </c>
       <c r="O14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>97</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" t="s">
+        <v>102</v>
+      </c>
+      <c r="F15" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" t="s">
+        <v>103</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" t="s">
+        <v>46</v>
+      </c>
+      <c r="J15" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K15" t="s">
+        <v>101</v>
+      </c>
+      <c r="L15" s="4">
+        <v>100</v>
+      </c>
+      <c r="M15" s="4">
+        <v>900</v>
+      </c>
+      <c r="N15" s="4">
+        <v>369</v>
+      </c>
+      <c r="O15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>102</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K16" t="s">
+        <v>101</v>
+      </c>
+      <c r="L16" s="4">
+        <v>100</v>
+      </c>
+      <c r="M16" s="4">
+        <v>900</v>
+      </c>
+      <c r="N16" s="4">
+        <v>369</v>
+      </c>
+      <c r="O16" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E17" t="s">
+    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
+      <c r="E18" t="s">
         <v>89</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{584731D3-684E-4EDD-AA21-197729E55E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B520A3B-5D98-49DA-9DFD-555F41B3130E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="107">
   <si>
     <t>Matrix</t>
   </si>
@@ -362,6 +362,9 @@
   </si>
   <si>
     <t>5123450000000008</t>
+  </si>
+  <si>
+    <t>4242424242424242</t>
   </si>
 </sst>
 </file>
@@ -786,7 +789,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" customWidth="1"/>
@@ -1555,11 +1558,58 @@
         <v>369</v>
       </c>
       <c r="O16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E17" t="s">
+        <v>102</v>
+      </c>
+      <c r="F17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" t="s">
+        <v>103</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K17" t="s">
+        <v>101</v>
+      </c>
+      <c r="L17" s="4">
+        <v>100</v>
+      </c>
+      <c r="M17" s="4">
+        <v>900</v>
+      </c>
+      <c r="N17" s="4">
+        <v>369</v>
+      </c>
+      <c r="O17" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="5:5" x14ac:dyDescent="0.35">
-      <c r="E18" t="s">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E19" t="s">
         <v>89</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B520A3B-5D98-49DA-9DFD-555F41B3130E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE248E48-393C-4487-A09C-3FA3119F3A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="111">
   <si>
     <t>Matrix</t>
   </si>
@@ -365,6 +365,18 @@
   </si>
   <si>
     <t>4242424242424242</t>
+  </si>
+  <si>
+    <t>Varun chakravarti</t>
+  </si>
+  <si>
+    <t>exactly</t>
+  </si>
+  <si>
+    <t>exactlypay-mid</t>
+  </si>
+  <si>
+    <t>4000000000003220</t>
   </si>
 </sst>
 </file>
@@ -789,10 +801,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" style="4" customWidth="1"/>
@@ -1558,7 +1570,7 @@
         <v>369</v>
       </c>
       <c r="O16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
@@ -1605,11 +1617,58 @@
         <v>369</v>
       </c>
       <c r="O17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" t="s">
+        <v>108</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" t="s">
+        <v>46</v>
+      </c>
+      <c r="J18" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K18" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="L18" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="E19" t="s">
+      <c r="M18" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N18" s="4">
+        <v>999</v>
+      </c>
+      <c r="O18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="E20" t="s">
         <v>89</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE248E48-393C-4487-A09C-3FA3119F3A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47EF115-0C22-4C32-998D-8946646F0ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1429,7 +1429,7 @@
         <v>569</v>
       </c>
       <c r="O13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
@@ -1570,7 +1570,7 @@
         <v>369</v>
       </c>
       <c r="O16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47EF115-0C22-4C32-998D-8946646F0ED3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307FF7EE-B607-4902-8677-5FB3C7D0E8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="118">
   <si>
     <t>Matrix</t>
   </si>
@@ -313,9 +313,6 @@
     <t>4900490000000576</t>
   </si>
   <si>
-    <t>`</t>
-  </si>
-  <si>
     <t>4100000000000100</t>
   </si>
   <si>
@@ -377,6 +374,30 @@
   </si>
   <si>
     <t>4000000000003220</t>
+  </si>
+  <si>
+    <t>4176660000000118</t>
+  </si>
+  <si>
+    <t>shift4</t>
+  </si>
+  <si>
+    <t>4176660000000092</t>
+  </si>
+  <si>
+    <t>4176660000000068</t>
+  </si>
+  <si>
+    <t>shift4-mid</t>
+  </si>
+  <si>
+    <t>shift4Frictionless</t>
+  </si>
+  <si>
+    <t>4176660000000027</t>
+  </si>
+  <si>
+    <t>4176660000000134</t>
   </si>
 </sst>
 </file>
@@ -473,7 +494,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -499,6 +520,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -801,10 +826,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.36328125" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" style="4" customWidth="1"/>
@@ -822,7 +847,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+      <c r="A1" s="18" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
@@ -869,7 +894,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" s="18" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -916,7 +941,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="18" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -963,7 +988,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1010,7 +1035,7 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1057,7 +1082,7 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1104,7 +1129,7 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1151,7 +1176,7 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+      <c r="A8" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1198,7 +1223,7 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+      <c r="A9" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -1245,7 +1270,7 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+      <c r="A10" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1292,7 +1317,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+      <c r="A11" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
@@ -1339,7 +1364,7 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+      <c r="A12" s="18" t="s">
         <v>87</v>
       </c>
       <c r="B12" s="3" t="s">
@@ -1386,20 +1411,20 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>94</v>
+      <c r="A13" s="18" t="s">
+        <v>93</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" t="s">
         <v>92</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E13" t="s">
-        <v>93</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
@@ -1417,7 +1442,7 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L13" s="4">
         <v>100</v>
@@ -1429,24 +1454,24 @@
         <v>569</v>
       </c>
       <c r="O13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
+      <c r="A14" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="C14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E14" t="s">
         <v>95</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="E14" t="s">
-        <v>96</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
@@ -1464,7 +1489,7 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L14" s="4">
         <v>100</v>
@@ -1480,26 +1505,26 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
+      <c r="A15" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>99</v>
-      </c>
       <c r="E15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>56</v>
@@ -1511,7 +1536,7 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L15" s="4">
         <v>100</v>
@@ -1527,26 +1552,26 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
+      <c r="A16" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>56</v>
@@ -1558,7 +1583,7 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L16" s="4">
         <v>100</v>
@@ -1574,26 +1599,26 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>104</v>
+      <c r="A17" s="18" t="s">
+        <v>103</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>56</v>
@@ -1605,7 +1630,7 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L17" s="4">
         <v>100</v>
@@ -1621,20 +1646,20 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
+      <c r="A18" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" t="s">
         <v>107</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s">
-        <v>108</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -1652,7 +1677,7 @@
         <v>54</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="L18" s="4">
         <v>1</v>
@@ -1667,12 +1692,243 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" t="s">
+        <v>111</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" t="s">
+        <v>21</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" t="s">
+        <v>46</v>
+      </c>
+      <c r="J19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K19" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L19" s="4">
+        <v>1</v>
+      </c>
+      <c r="M19" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N19" s="4">
+        <v>999</v>
+      </c>
+      <c r="O19" t="b">
+        <v>1</v>
+      </c>
+    </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>98</v>
+      </c>
       <c r="E20" t="s">
-        <v>89</v>
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I20" t="s">
+        <v>46</v>
+      </c>
+      <c r="J20" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K20" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L20" s="4">
+        <v>1</v>
+      </c>
+      <c r="M20" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N20" s="4">
+        <v>999</v>
+      </c>
+      <c r="O20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" t="s">
+        <v>72</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I21" t="s">
+        <v>46</v>
+      </c>
+      <c r="J21" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K21" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L21" s="4">
+        <v>1</v>
+      </c>
+      <c r="M21" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N21" s="4">
+        <v>999</v>
+      </c>
+      <c r="O21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E22" t="s">
+        <v>115</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" t="s">
+        <v>46</v>
+      </c>
+      <c r="J22" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K22" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L22" s="4">
+        <v>1</v>
+      </c>
+      <c r="M22" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N22" s="4">
+        <v>999</v>
+      </c>
+      <c r="O22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E23" t="s">
+        <v>111</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" t="s">
+        <v>72</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I23" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K23" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L23" s="4">
+        <v>1</v>
+      </c>
+      <c r="M23" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N23" s="4">
+        <v>999</v>
+      </c>
+      <c r="O23" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307FF7EE-B607-4902-8677-5FB3C7D0E8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1E3CA2-2029-438D-BBB6-404A1474224F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="123">
   <si>
     <t>Matrix</t>
   </si>
@@ -398,6 +398,21 @@
   </si>
   <si>
     <t>4176660000000134</t>
+  </si>
+  <si>
+    <t>5204730000001011</t>
+  </si>
+  <si>
+    <t>5299910010000015</t>
+  </si>
+  <si>
+    <t>5299990270000392</t>
+  </si>
+  <si>
+    <t>5299990270000368</t>
+  </si>
+  <si>
+    <t>5299990270000590</t>
   </si>
 </sst>
 </file>
@@ -826,7 +841,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
@@ -1736,7 +1751,7 @@
         <v>999</v>
       </c>
       <c r="O19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -1783,7 +1798,7 @@
         <v>999</v>
       </c>
       <c r="O20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -1830,7 +1845,7 @@
         <v>999</v>
       </c>
       <c r="O21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
@@ -1877,7 +1892,7 @@
         <v>999</v>
       </c>
       <c r="O22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
@@ -1924,6 +1939,241 @@
         <v>999</v>
       </c>
       <c r="O23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" t="s">
+        <v>111</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>21</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I24" t="s">
+        <v>46</v>
+      </c>
+      <c r="J24" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K24" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L24" s="4">
+        <v>100</v>
+      </c>
+      <c r="M24" s="4">
+        <v>900</v>
+      </c>
+      <c r="N24" s="4">
+        <v>249</v>
+      </c>
+      <c r="O24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" t="s">
+        <v>111</v>
+      </c>
+      <c r="F25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G25" t="s">
+        <v>21</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I25" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K25" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L25" s="4">
+        <v>100</v>
+      </c>
+      <c r="M25" s="4">
+        <v>900</v>
+      </c>
+      <c r="N25" s="4">
+        <v>249</v>
+      </c>
+      <c r="O25" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E26" t="s">
+        <v>111</v>
+      </c>
+      <c r="F26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" t="s">
+        <v>21</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I26" t="s">
+        <v>46</v>
+      </c>
+      <c r="J26" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K26" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L26" s="4">
+        <v>100</v>
+      </c>
+      <c r="M26" s="4">
+        <v>900</v>
+      </c>
+      <c r="N26" s="4">
+        <v>249</v>
+      </c>
+      <c r="O26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E27" t="s">
+        <v>111</v>
+      </c>
+      <c r="F27" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I27" t="s">
+        <v>46</v>
+      </c>
+      <c r="J27" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K27" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L27" s="4">
+        <v>100</v>
+      </c>
+      <c r="M27" s="4">
+        <v>900</v>
+      </c>
+      <c r="N27" s="4">
+        <v>249</v>
+      </c>
+      <c r="O27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E28" t="s">
+        <v>111</v>
+      </c>
+      <c r="F28" t="s">
+        <v>16</v>
+      </c>
+      <c r="G28" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I28" t="s">
+        <v>46</v>
+      </c>
+      <c r="J28" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K28" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L28" s="4">
+        <v>100</v>
+      </c>
+      <c r="M28" s="4">
+        <v>900</v>
+      </c>
+      <c r="N28" s="4">
+        <v>249</v>
+      </c>
+      <c r="O28" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1E3CA2-2029-438D-BBB6-404A1474224F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574F9C53-1443-4D5D-8D85-A135A98FEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1959,7 +1959,7 @@
         <v>111</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G24" t="s">
         <v>21</v>
@@ -2006,7 +2006,7 @@
         <v>111</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G25" t="s">
         <v>21</v>
@@ -2053,7 +2053,7 @@
         <v>111</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G26" t="s">
         <v>21</v>
@@ -2100,7 +2100,7 @@
         <v>111</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" t="s">
         <v>21</v>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{574F9C53-1443-4D5D-8D85-A135A98FEA22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD576AB-836C-4773-AAEB-39E50160FCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="126">
   <si>
     <t>Matrix</t>
   </si>
@@ -413,6 +413,15 @@
   </si>
   <si>
     <t>5299990270000590</t>
+  </si>
+  <si>
+    <t>4012000033330026</t>
+  </si>
+  <si>
+    <t>payaza-card</t>
+  </si>
+  <si>
+    <t>NGN</t>
   </si>
 </sst>
 </file>
@@ -841,7 +850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
@@ -1986,7 +1995,7 @@
         <v>249</v>
       </c>
       <c r="O24" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
@@ -2033,7 +2042,7 @@
         <v>249</v>
       </c>
       <c r="O25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
@@ -2080,7 +2089,7 @@
         <v>249</v>
       </c>
       <c r="O26" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
@@ -2127,7 +2136,7 @@
         <v>249</v>
       </c>
       <c r="O27" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
@@ -2174,6 +2183,100 @@
         <v>249</v>
       </c>
       <c r="O28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E29" t="s">
+        <v>124</v>
+      </c>
+      <c r="F29" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" t="s">
+        <v>46</v>
+      </c>
+      <c r="J29" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K29" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="L29" s="4">
+        <v>100</v>
+      </c>
+      <c r="M29" s="4">
+        <v>900</v>
+      </c>
+      <c r="N29" s="4">
+        <v>249</v>
+      </c>
+      <c r="O29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E30" t="s">
+        <v>124</v>
+      </c>
+      <c r="F30" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" t="s">
+        <v>125</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I30" t="s">
+        <v>46</v>
+      </c>
+      <c r="J30" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K30" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="L30" s="4">
+        <v>100</v>
+      </c>
+      <c r="M30" s="4">
+        <v>900</v>
+      </c>
+      <c r="N30" s="4">
+        <v>249</v>
+      </c>
+      <c r="O30" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AD576AB-836C-4773-AAEB-39E50160FCEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8A9D31-1278-4B44-B617-AA8D85B6EA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="129">
   <si>
     <t>Matrix</t>
   </si>
@@ -422,6 +422,15 @@
   </si>
   <si>
     <t>NGN</t>
+  </si>
+  <si>
+    <t>payable-pix</t>
+  </si>
+  <si>
+    <t>4149011500000147</t>
+  </si>
+  <si>
+    <t>Hazma Sher A Baloch</t>
   </si>
 </sst>
 </file>
@@ -850,7 +859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
@@ -2230,7 +2239,7 @@
         <v>249</v>
       </c>
       <c r="O29" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
@@ -2277,6 +2286,53 @@
         <v>249</v>
       </c>
       <c r="O30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F31" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" t="s">
+        <v>21</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I31" t="s">
+        <v>46</v>
+      </c>
+      <c r="J31" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K31" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="L31" s="4">
+        <v>1</v>
+      </c>
+      <c r="M31" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N31" s="4">
+        <v>999</v>
+      </c>
+      <c r="O31" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A8A9D31-1278-4B44-B617-AA8D85B6EA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA10BC9-65B8-46A8-866A-917E34B0881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="150">
   <si>
     <t>Matrix</t>
   </si>
@@ -430,7 +430,70 @@
     <t>4149011500000147</t>
   </si>
   <si>
-    <t>Hazma Sher A Baloch</t>
+    <t>5232050000010003</t>
+  </si>
+  <si>
+    <t>Hamza Sher A Baloch</t>
+  </si>
+  <si>
+    <t>4024007119078466</t>
+  </si>
+  <si>
+    <t>4532904789286871</t>
+  </si>
+  <si>
+    <t>12/30</t>
+  </si>
+  <si>
+    <t>4012001037484447</t>
+  </si>
+  <si>
+    <t>12/31</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>12/32</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>4012001037461114</t>
+  </si>
+  <si>
+    <t>4242000000000000</t>
+  </si>
+  <si>
+    <t>4012001038443335</t>
+  </si>
+  <si>
+    <t>12/33</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>12/34</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>12/35</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>4242424242420000</t>
+  </si>
+  <si>
+    <t>4012001038488884</t>
+  </si>
+  <si>
+    <t>4242426790614587</t>
   </si>
 </sst>
 </file>
@@ -859,7 +922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
@@ -2291,16 +2354,16 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="18" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>127</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="E31" t="s">
         <v>126</v>
@@ -2320,8 +2383,8 @@
       <c r="J31" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K31" s="15" t="s">
-        <v>114</v>
+      <c r="K31" t="s">
+        <v>126</v>
       </c>
       <c r="L31" s="4">
         <v>1</v>
@@ -2333,6 +2396,476 @@
         <v>999</v>
       </c>
       <c r="O31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" t="s">
+        <v>126</v>
+      </c>
+      <c r="F32" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" t="s">
+        <v>21</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I32" t="s">
+        <v>46</v>
+      </c>
+      <c r="J32" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K32" t="s">
+        <v>126</v>
+      </c>
+      <c r="L32" s="4">
+        <v>1</v>
+      </c>
+      <c r="M32" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N32" s="4">
+        <v>999</v>
+      </c>
+      <c r="O32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" t="s">
+        <v>126</v>
+      </c>
+      <c r="F33" t="s">
+        <v>12</v>
+      </c>
+      <c r="G33" t="s">
+        <v>21</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" t="s">
+        <v>46</v>
+      </c>
+      <c r="J33" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" t="s">
+        <v>126</v>
+      </c>
+      <c r="L33" s="4">
+        <v>1</v>
+      </c>
+      <c r="M33" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N33" s="4">
+        <v>999</v>
+      </c>
+      <c r="O33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E34" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" t="s">
+        <v>21</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I34" t="s">
+        <v>46</v>
+      </c>
+      <c r="J34" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K34" t="s">
+        <v>126</v>
+      </c>
+      <c r="L34" s="4">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N34" s="4">
+        <v>999</v>
+      </c>
+      <c r="O34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E35" t="s">
+        <v>126</v>
+      </c>
+      <c r="F35" t="s">
+        <v>12</v>
+      </c>
+      <c r="G35" t="s">
+        <v>21</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I35" t="s">
+        <v>46</v>
+      </c>
+      <c r="J35" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" t="s">
+        <v>126</v>
+      </c>
+      <c r="L35" s="4">
+        <v>1</v>
+      </c>
+      <c r="M35" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N35" s="4">
+        <v>249</v>
+      </c>
+      <c r="O35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" t="s">
+        <v>12</v>
+      </c>
+      <c r="G36" t="s">
+        <v>21</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" t="s">
+        <v>46</v>
+      </c>
+      <c r="J36" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" t="s">
+        <v>126</v>
+      </c>
+      <c r="L36" s="4">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N36" s="4">
+        <v>249</v>
+      </c>
+      <c r="O36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E37" t="s">
+        <v>126</v>
+      </c>
+      <c r="F37" t="s">
+        <v>12</v>
+      </c>
+      <c r="G37" t="s">
+        <v>21</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I37" t="s">
+        <v>46</v>
+      </c>
+      <c r="J37" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37" t="s">
+        <v>126</v>
+      </c>
+      <c r="L37" s="4">
+        <v>1</v>
+      </c>
+      <c r="M37" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N37" s="4">
+        <v>249</v>
+      </c>
+      <c r="O37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E38" t="s">
+        <v>126</v>
+      </c>
+      <c r="F38" t="s">
+        <v>12</v>
+      </c>
+      <c r="G38" t="s">
+        <v>21</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I38" t="s">
+        <v>46</v>
+      </c>
+      <c r="J38" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K38" t="s">
+        <v>126</v>
+      </c>
+      <c r="L38" s="4">
+        <v>1</v>
+      </c>
+      <c r="M38" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N38" s="4">
+        <v>249</v>
+      </c>
+      <c r="O38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" t="s">
+        <v>126</v>
+      </c>
+      <c r="F39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" t="s">
+        <v>21</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I39" t="s">
+        <v>46</v>
+      </c>
+      <c r="J39" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K39" t="s">
+        <v>126</v>
+      </c>
+      <c r="L39" s="4">
+        <v>1</v>
+      </c>
+      <c r="M39" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N39" s="4">
+        <v>249</v>
+      </c>
+      <c r="O39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E40" t="s">
+        <v>126</v>
+      </c>
+      <c r="F40" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" t="s">
+        <v>21</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I40" t="s">
+        <v>46</v>
+      </c>
+      <c r="J40" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K40" t="s">
+        <v>126</v>
+      </c>
+      <c r="L40" s="4">
+        <v>1</v>
+      </c>
+      <c r="M40" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N40" s="4">
+        <v>249</v>
+      </c>
+      <c r="O40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" t="s">
+        <v>126</v>
+      </c>
+      <c r="F41" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" t="s">
+        <v>21</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I41" t="s">
+        <v>46</v>
+      </c>
+      <c r="J41" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K41" t="s">
+        <v>126</v>
+      </c>
+      <c r="L41" s="4">
+        <v>1</v>
+      </c>
+      <c r="M41" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N41" s="4">
+        <v>249</v>
+      </c>
+      <c r="O41" t="b">
         <v>1</v>
       </c>
     </row>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AA10BC9-65B8-46A8-866A-917E34B0881F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23631A34-75CF-466D-81CD-DE5FE35C79B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="151">
   <si>
     <t>Matrix</t>
   </si>
@@ -250,12 +250,6 @@
     <t>123</t>
   </si>
   <si>
-    <t>CAD</t>
-  </si>
-  <si>
-    <t>INTERAC</t>
-  </si>
-  <si>
     <t>4387751111111111</t>
   </si>
   <si>
@@ -494,6 +488,15 @@
   </si>
   <si>
     <t>4242426790614587</t>
+  </si>
+  <si>
+    <t>5105105105105100</t>
+  </si>
+  <si>
+    <t>5555555555554444</t>
+  </si>
+  <si>
+    <t>5454545454545454</t>
   </si>
 </sst>
 </file>
@@ -590,7 +593,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -613,7 +616,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -922,10 +924,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O44"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="25.36328125" style="18" customWidth="1"/>
+    <col min="1" max="1" width="25.36328125" style="17" customWidth="1"/>
     <col min="2" max="2" width="21.54296875" customWidth="1"/>
     <col min="3" max="3" width="11.81640625" customWidth="1"/>
     <col min="4" max="4" width="10.7265625" style="4" customWidth="1"/>
@@ -943,7 +945,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B1" t="s">
@@ -990,7 +992,7 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>26</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -1037,7 +1039,7 @@
       </c>
     </row>
     <row r="3" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="18" t="s">
+      <c r="A3" s="17" t="s">
         <v>58</v>
       </c>
       <c r="B3" s="5" t="s">
@@ -1067,7 +1069,7 @@
       <c r="J3" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="14" t="s">
         <v>60</v>
       </c>
       <c r="L3" s="4">
@@ -1084,7 +1086,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -1099,11 +1101,11 @@
       <c r="E4" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="14" t="s">
-        <v>69</v>
+      <c r="F4" t="s">
+        <v>12</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>56</v>
@@ -1131,11 +1133,11 @@
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="18" t="s">
+      <c r="A5" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>66</v>
@@ -1144,13 +1146,13 @@
         <v>67</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>56</v>
@@ -1162,7 +1164,7 @@
         <v>54</v>
       </c>
       <c r="K5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="L5" s="4">
         <v>10</v>
@@ -1178,11 +1180,11 @@
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>66</v>
@@ -1191,13 +1193,13 @@
         <v>67</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>56</v>
@@ -1208,8 +1210,8 @@
       <c r="J6" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K6" s="15" t="s">
-        <v>76</v>
+      <c r="K6" s="14" t="s">
+        <v>74</v>
       </c>
       <c r="L6" s="4">
         <v>100</v>
@@ -1225,11 +1227,11 @@
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>66</v>
@@ -1237,14 +1239,14 @@
       <c r="D7" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E7" s="15" t="s">
-        <v>81</v>
+      <c r="E7" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>56</v>
@@ -1255,8 +1257,8 @@
       <c r="J7" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K7" s="16" t="s">
-        <v>78</v>
+      <c r="K7" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="L7" s="4">
         <v>100</v>
@@ -1272,11 +1274,11 @@
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="18" t="s">
+      <c r="A8" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>66</v>
@@ -1284,14 +1286,14 @@
       <c r="D8" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="15" t="s">
-        <v>81</v>
+      <c r="E8" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="F8" t="s">
         <v>12</v>
       </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>56</v>
@@ -1302,8 +1304,8 @@
       <c r="J8" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K8" s="16" t="s">
-        <v>78</v>
+      <c r="K8" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="L8" s="4">
         <v>100</v>
@@ -1319,11 +1321,11 @@
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="18" t="s">
+      <c r="A9" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>66</v>
@@ -1331,14 +1333,14 @@
       <c r="D9" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E9" s="15" t="s">
-        <v>81</v>
+      <c r="E9" s="14" t="s">
+        <v>79</v>
       </c>
       <c r="F9" t="s">
         <v>12</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>56</v>
@@ -1349,8 +1351,8 @@
       <c r="J9" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K9" s="16" t="s">
-        <v>78</v>
+      <c r="K9" s="15" t="s">
+        <v>76</v>
       </c>
       <c r="L9" s="4">
         <v>100</v>
@@ -1366,11 +1368,11 @@
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>66</v>
@@ -1379,13 +1381,13 @@
         <v>67</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" t="s">
         <v>12</v>
       </c>
       <c r="G10" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>56</v>
@@ -1396,8 +1398,8 @@
       <c r="J10" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K10" s="16" t="s">
-        <v>83</v>
+      <c r="K10" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="L10" s="4">
         <v>100</v>
@@ -1413,11 +1415,11 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>66</v>
@@ -1426,13 +1428,13 @@
         <v>67</v>
       </c>
       <c r="E11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F11" t="s">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>56</v>
@@ -1443,8 +1445,8 @@
       <c r="J11" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K11" s="16" t="s">
-        <v>83</v>
+      <c r="K11" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="L11" s="4">
         <v>100</v>
@@ -1460,11 +1462,11 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="18" t="s">
-        <v>87</v>
+      <c r="A12" s="17" t="s">
+        <v>85</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>66</v>
@@ -1473,13 +1475,13 @@
         <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F12" t="s">
         <v>12</v>
       </c>
       <c r="G12" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>56</v>
@@ -1490,8 +1492,8 @@
       <c r="J12" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K12" s="16" t="s">
-        <v>83</v>
+      <c r="K12" s="15" t="s">
+        <v>81</v>
       </c>
       <c r="L12" s="4">
         <v>100</v>
@@ -1507,26 +1509,26 @@
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="18" t="s">
-        <v>93</v>
+      <c r="A13" s="17" t="s">
+        <v>91</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" t="s">
         <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>92</v>
       </c>
       <c r="F13" t="s">
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>56</v>
@@ -1538,7 +1540,7 @@
         <v>54</v>
       </c>
       <c r="K13" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L13" s="4">
         <v>100</v>
@@ -1554,26 +1556,26 @@
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E14" t="s">
         <v>93</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>95</v>
       </c>
       <c r="F14" t="s">
         <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>56</v>
@@ -1585,7 +1587,7 @@
         <v>54</v>
       </c>
       <c r="K14" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L14" s="4">
         <v>100</v>
@@ -1601,26 +1603,26 @@
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="E15" t="s">
         <v>99</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E15" t="s">
-        <v>101</v>
       </c>
       <c r="F15" t="s">
         <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>56</v>
@@ -1632,7 +1634,7 @@
         <v>54</v>
       </c>
       <c r="K15" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L15" s="4">
         <v>100</v>
@@ -1648,26 +1650,26 @@
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
-        <v>103</v>
+      <c r="A16" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" t="s">
         <v>99</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" t="s">
-        <v>101</v>
       </c>
       <c r="F16" t="s">
         <v>16</v>
       </c>
       <c r="G16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>56</v>
@@ -1679,7 +1681,7 @@
         <v>54</v>
       </c>
       <c r="K16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L16" s="4">
         <v>100</v>
@@ -1695,26 +1697,26 @@
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="18" t="s">
+      <c r="A17" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="C17" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" t="s">
         <v>99</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E17" t="s">
-        <v>101</v>
       </c>
       <c r="F17" t="s">
         <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>56</v>
@@ -1726,7 +1728,7 @@
         <v>54</v>
       </c>
       <c r="K17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="L17" s="4">
         <v>100</v>
@@ -1742,20 +1744,20 @@
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="18" t="s">
-        <v>106</v>
+      <c r="A18" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F18" t="s">
         <v>12</v>
@@ -1772,8 +1774,8 @@
       <c r="J18" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K18" s="15" t="s">
-        <v>108</v>
+      <c r="K18" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="L18" s="4">
         <v>1</v>
@@ -1789,20 +1791,20 @@
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>110</v>
+      <c r="A19" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>108</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F19" t="s">
         <v>12</v>
@@ -1819,8 +1821,8 @@
       <c r="J19" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K19" s="15" t="s">
-        <v>114</v>
+      <c r="K19" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L19" s="4">
         <v>1</v>
@@ -1836,20 +1838,20 @@
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="18" t="s">
-        <v>106</v>
+      <c r="A20" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E20" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F20" t="s">
         <v>12</v>
@@ -1866,8 +1868,8 @@
       <c r="J20" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K20" s="15" t="s">
-        <v>114</v>
+      <c r="K20" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L20" s="4">
         <v>1</v>
@@ -1883,26 +1885,26 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="18" t="s">
-        <v>106</v>
+      <c r="A21" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" t="s">
         <v>113</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E21" t="s">
-        <v>115</v>
       </c>
       <c r="F21" t="s">
         <v>12</v>
       </c>
       <c r="G21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>56</v>
@@ -1913,8 +1915,8 @@
       <c r="J21" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K21" s="15" t="s">
-        <v>114</v>
+      <c r="K21" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L21" s="4">
         <v>1</v>
@@ -1930,26 +1932,26 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="18" t="s">
-        <v>106</v>
+      <c r="A22" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E22" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s">
         <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>56</v>
@@ -1960,8 +1962,8 @@
       <c r="J22" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K22" s="15" t="s">
-        <v>114</v>
+      <c r="K22" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L22" s="4">
         <v>1</v>
@@ -1977,26 +1979,26 @@
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="18" t="s">
-        <v>106</v>
+      <c r="A23" s="17" t="s">
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F23" t="s">
         <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>56</v>
@@ -2007,8 +2009,8 @@
       <c r="J23" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>114</v>
+      <c r="K23" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L23" s="4">
         <v>1</v>
@@ -2024,11 +2026,11 @@
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="18" t="s">
+      <c r="A24" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>66</v>
@@ -2037,7 +2039,7 @@
         <v>67</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F24" t="s">
         <v>16</v>
@@ -2054,8 +2056,8 @@
       <c r="J24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K24" s="15" t="s">
-        <v>114</v>
+      <c r="K24" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L24" s="4">
         <v>100</v>
@@ -2071,11 +2073,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="18" t="s">
+      <c r="A25" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>66</v>
@@ -2084,7 +2086,7 @@
         <v>67</v>
       </c>
       <c r="E25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F25" t="s">
         <v>16</v>
@@ -2101,8 +2103,8 @@
       <c r="J25" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K25" s="15" t="s">
-        <v>114</v>
+      <c r="K25" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L25" s="4">
         <v>100</v>
@@ -2118,11 +2120,11 @@
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="18" t="s">
+      <c r="A26" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>66</v>
@@ -2131,7 +2133,7 @@
         <v>67</v>
       </c>
       <c r="E26" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F26" t="s">
         <v>16</v>
@@ -2148,8 +2150,8 @@
       <c r="J26" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K26" s="15" t="s">
-        <v>114</v>
+      <c r="K26" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L26" s="4">
         <v>100</v>
@@ -2165,11 +2167,11 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="18" t="s">
+      <c r="A27" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>66</v>
@@ -2178,7 +2180,7 @@
         <v>67</v>
       </c>
       <c r="E27" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
         <v>16</v>
@@ -2195,8 +2197,8 @@
       <c r="J27" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K27" s="15" t="s">
-        <v>114</v>
+      <c r="K27" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L27" s="4">
         <v>100</v>
@@ -2212,11 +2214,11 @@
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="18" t="s">
+      <c r="A28" s="17" t="s">
         <v>17</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>66</v>
@@ -2225,7 +2227,7 @@
         <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
         <v>16</v>
@@ -2242,8 +2244,8 @@
       <c r="J28" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K28" s="15" t="s">
-        <v>114</v>
+      <c r="K28" s="14" t="s">
+        <v>112</v>
       </c>
       <c r="L28" s="4">
         <v>100</v>
@@ -2259,26 +2261,26 @@
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="17" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E29" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F29" t="s">
         <v>12</v>
       </c>
       <c r="G29" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>56</v>
@@ -2289,8 +2291,8 @@
       <c r="J29" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K29" s="15" t="s">
-        <v>124</v>
+      <c r="K29" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="L29" s="4">
         <v>100</v>
@@ -2306,26 +2308,26 @@
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="17" t="s">
         <v>27</v>
       </c>
       <c r="B30" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E30" t="s">
         <v>122</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="E30" t="s">
-        <v>124</v>
       </c>
       <c r="F30" t="s">
         <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>56</v>
@@ -2336,8 +2338,8 @@
       <c r="J30" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>124</v>
+      <c r="K30" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="L30" s="4">
         <v>100</v>
@@ -2353,11 +2355,11 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="18" t="s">
-        <v>129</v>
+      <c r="A31" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>66</v>
@@ -2366,7 +2368,7 @@
         <v>67</v>
       </c>
       <c r="E31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F31" t="s">
         <v>12</v>
@@ -2384,7 +2386,7 @@
         <v>54</v>
       </c>
       <c r="K31" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L31" s="4">
         <v>1</v>
@@ -2396,15 +2398,15 @@
         <v>999</v>
       </c>
       <c r="O31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="18" t="s">
-        <v>129</v>
+      <c r="A32" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>66</v>
@@ -2413,7 +2415,7 @@
         <v>67</v>
       </c>
       <c r="E32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F32" t="s">
         <v>16</v>
@@ -2431,7 +2433,7 @@
         <v>54</v>
       </c>
       <c r="K32" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L32" s="4">
         <v>1</v>
@@ -2447,11 +2449,11 @@
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="18" t="s">
-        <v>129</v>
+      <c r="A33" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>66</v>
@@ -2460,7 +2462,7 @@
         <v>67</v>
       </c>
       <c r="E33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F33" t="s">
         <v>12</v>
@@ -2478,7 +2480,7 @@
         <v>54</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L33" s="4">
         <v>1</v>
@@ -2494,20 +2496,20 @@
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="C34" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F34" t="s">
         <v>12</v>
@@ -2525,7 +2527,7 @@
         <v>54</v>
       </c>
       <c r="K34" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L34" s="4">
         <v>1</v>
@@ -2541,20 +2543,20 @@
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="18" t="s">
-        <v>129</v>
+      <c r="A35" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F35" t="s">
         <v>12</v>
@@ -2572,7 +2574,7 @@
         <v>54</v>
       </c>
       <c r="K35" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L35" s="4">
         <v>1</v>
@@ -2584,24 +2586,24 @@
         <v>249</v>
       </c>
       <c r="O35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="18" t="s">
-        <v>129</v>
+      <c r="A36" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D36" s="5" t="s">
         <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F36" t="s">
         <v>12</v>
@@ -2619,7 +2621,7 @@
         <v>54</v>
       </c>
       <c r="K36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L36" s="4">
         <v>1</v>
@@ -2631,24 +2633,24 @@
         <v>249</v>
       </c>
       <c r="O36" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="18" t="s">
-        <v>129</v>
+      <c r="A37" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F37" t="s">
         <v>12</v>
@@ -2666,7 +2668,7 @@
         <v>54</v>
       </c>
       <c r="K37" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L37" s="4">
         <v>1</v>
@@ -2678,24 +2680,24 @@
         <v>249</v>
       </c>
       <c r="O37" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="18" t="s">
-        <v>129</v>
+      <c r="A38" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F38" t="s">
         <v>12</v>
@@ -2713,7 +2715,7 @@
         <v>54</v>
       </c>
       <c r="K38" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L38" s="4">
         <v>1</v>
@@ -2725,24 +2727,24 @@
         <v>249</v>
       </c>
       <c r="O38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="18" t="s">
-        <v>129</v>
+      <c r="A39" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F39" t="s">
         <v>12</v>
@@ -2760,7 +2762,7 @@
         <v>54</v>
       </c>
       <c r="K39" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L39" s="4">
         <v>1</v>
@@ -2772,24 +2774,24 @@
         <v>249</v>
       </c>
       <c r="O39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="18" t="s">
-        <v>129</v>
+      <c r="A40" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F40" t="s">
         <v>12</v>
@@ -2807,7 +2809,7 @@
         <v>54</v>
       </c>
       <c r="K40" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L40" s="4">
         <v>1</v>
@@ -2819,24 +2821,24 @@
         <v>249</v>
       </c>
       <c r="O40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="18" t="s">
-        <v>129</v>
+      <c r="A41" s="17" t="s">
+        <v>127</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F41" t="s">
         <v>12</v>
@@ -2854,7 +2856,7 @@
         <v>54</v>
       </c>
       <c r="K41" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="L41" s="4">
         <v>1</v>
@@ -2866,7 +2868,148 @@
         <v>249</v>
       </c>
       <c r="O41" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E42" t="s">
+        <v>124</v>
+      </c>
+      <c r="F42" t="s">
+        <v>16</v>
+      </c>
+      <c r="G42" t="s">
+        <v>21</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I42" t="s">
+        <v>46</v>
+      </c>
+      <c r="J42" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K42" t="s">
+        <v>124</v>
+      </c>
+      <c r="L42" s="4">
+        <v>1</v>
+      </c>
+      <c r="M42" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N42" s="4">
+        <v>249</v>
+      </c>
+      <c r="O42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" t="s">
+        <v>124</v>
+      </c>
+      <c r="F43" t="s">
+        <v>16</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I43" t="s">
+        <v>46</v>
+      </c>
+      <c r="J43" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K43" t="s">
+        <v>124</v>
+      </c>
+      <c r="L43" s="4">
+        <v>1</v>
+      </c>
+      <c r="M43" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N43" s="4">
+        <v>249</v>
+      </c>
+      <c r="O43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E44" t="s">
+        <v>124</v>
+      </c>
+      <c r="F44" t="s">
+        <v>16</v>
+      </c>
+      <c r="G44" t="s">
+        <v>21</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I44" t="s">
+        <v>46</v>
+      </c>
+      <c r="J44" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K44" t="s">
+        <v>124</v>
+      </c>
+      <c r="L44" s="4">
+        <v>1</v>
+      </c>
+      <c r="M44" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N44" s="4">
+        <v>249</v>
+      </c>
+      <c r="O44" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23631A34-75CF-466D-81CD-DE5FE35C79B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E25A5-9BD9-4AB4-8FE1-DECDFF0DFAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="732" uniqueCount="154">
   <si>
     <t>Matrix</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>5454545454545454</t>
+  </si>
+  <si>
+    <t>5200000000000015</t>
+  </si>
+  <si>
+    <t>yoyapayPayin</t>
+  </si>
+  <si>
+    <t>Test Test</t>
   </si>
 </sst>
 </file>
@@ -924,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A047734-60A8-451A-B92F-500542A01A48}">
-  <dimension ref="A1:O44"/>
+  <dimension ref="A1:O46"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.36328125" style="17" customWidth="1"/>
@@ -2398,7 +2407,7 @@
         <v>999</v>
       </c>
       <c r="O31" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.35">
@@ -3010,6 +3019,100 @@
       </c>
       <c r="O44" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="E45" t="s">
+        <v>124</v>
+      </c>
+      <c r="F45" t="s">
+        <v>16</v>
+      </c>
+      <c r="G45" t="s">
+        <v>70</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I45" t="s">
+        <v>46</v>
+      </c>
+      <c r="J45" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K45" t="s">
+        <v>124</v>
+      </c>
+      <c r="L45" s="4">
+        <v>1</v>
+      </c>
+      <c r="M45" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N45" s="4">
+        <v>249</v>
+      </c>
+      <c r="O45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" t="s">
+        <v>152</v>
+      </c>
+      <c r="F46" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" t="s">
+        <v>21</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I46" t="s">
+        <v>46</v>
+      </c>
+      <c r="J46" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="L46" s="4">
+        <v>1</v>
+      </c>
+      <c r="M46" s="4">
+        <v>2500</v>
+      </c>
+      <c r="N46" s="4">
+        <v>123</v>
+      </c>
+      <c r="O46" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/src/test/resources/ExcelResultsFolder/Cards.xlsx
+++ b/src/test/resources/ExcelResultsFolder/Cards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\git\Integration\src\test\resources\ExcelResultsFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E25A5-9BD9-4AB4-8FE1-DECDFF0DFAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33CE1772-D6AA-42BC-A363-9D45B799D22C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3073,7 +3073,7 @@
         <v>153</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>130</v>
